--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Fecha</t>
   </si>
@@ -40,34 +40,46 @@
     <t>Notas</t>
   </si>
   <si>
-    <t>2026-05-22 18:53:41</t>
-  </si>
-  <si>
-    <t>master</t>
-  </si>
-  <si>
-    <t>89926ba</t>
+    <t>2026-05-22 19:22:25</t>
+  </si>
+  <si>
+    <t>fase-1-backend-base</t>
+  </si>
+  <si>
+    <t>0401d7e</t>
   </si>
   <si>
     <t>unit</t>
   </si>
   <si>
-    <t>Cierre Fase 10B post-merge a master</t>
-  </si>
-  <si>
-    <t>2026-05-22 18:53:42</t>
+    <t>Cierre Fase 10B post-merge a master (frontend)</t>
+  </si>
+  <si>
+    <t>2026-05-22 19:22:26</t>
   </si>
   <si>
     <t>e2e</t>
   </si>
   <si>
-    <t>2026-05-22 18:53:43</t>
+    <t>Cierre Fase 10B post-merge a master (frontend Playwright)</t>
+  </si>
+  <si>
+    <t>2026-05-22 19:22:27</t>
   </si>
   <si>
     <t>lighthouse</t>
   </si>
   <si>
     <t>Login build prod · Perf 99 · A11y 100 · BP 96 · SEO 100</t>
+  </si>
+  <si>
+    <t>2026-05-22 19:22:28</t>
+  </si>
+  <si>
+    <t>backend-unit</t>
+  </si>
+  <si>
+    <t>Cierre Fase 1A — backend base sin DB ni Auth real</t>
   </si>
 </sst>
 </file>
@@ -453,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -550,12 +562,12 @@
         <v>126.05</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -564,7 +576,7 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -579,7 +591,36 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>55</v>
+      </c>
+      <c r="F5">
+        <v>55</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>Fecha</t>
   </si>
@@ -80,6 +80,21 @@
   </si>
   <si>
     <t>Cierre Fase 1A — backend base sin DB ni Auth real</t>
+  </si>
+  <si>
+    <t>2026-05-23 00:26:49</t>
+  </si>
+  <si>
+    <t>fase-1-backend-local</t>
+  </si>
+  <si>
+    <t>6fd6922</t>
+  </si>
+  <si>
+    <t>backend-all</t>
+  </si>
+  <si>
+    <t>Cierre Fase 1B.2 — repos PostgreSQL (20 integration + 55 unit)</t>
   </si>
 </sst>
 </file>
@@ -465,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -623,6 +638,35 @@
         <v>22</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>75</v>
+      </c>
+      <c r="F6">
+        <v>75</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>3.05</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Fecha</t>
   </si>
@@ -95,6 +95,15 @@
   </si>
   <si>
     <t>Cierre Fase 1B.2 — repos PostgreSQL (20 integration + 55 unit)</t>
+  </si>
+  <si>
+    <t>2026-05-23 00:35:06</t>
+  </si>
+  <si>
+    <t>c26600d</t>
+  </si>
+  <si>
+    <t>Cierre Fase 1B.3 — dev auth provider + /auth/me end-to-end</t>
   </si>
 </sst>
 </file>
@@ -480,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -667,6 +676,35 @@
         <v>27</v>
       </c>
     </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>82</v>
+      </c>
+      <c r="F7">
+        <v>82</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>2.46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>Fecha</t>
   </si>
@@ -104,6 +104,15 @@
   </si>
   <si>
     <t>Cierre Fase 1B.3 — dev auth provider + /auth/me end-to-end</t>
+  </si>
+  <si>
+    <t>2026-05-23 00:43:44</t>
+  </si>
+  <si>
+    <t>deff913</t>
+  </si>
+  <si>
+    <t>Cierre Fase 1B.5 — endpoints CRUD (taxonomy + documents + sessions + dashboard)</t>
   </si>
 </sst>
 </file>
@@ -489,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -705,6 +714,35 @@
         <v>30</v>
       </c>
     </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>101</v>
+      </c>
+      <c r="F8">
+        <v>101</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>9.6</v>
+      </c>
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
   <si>
     <t>Fecha</t>
   </si>
@@ -113,6 +113,45 @@
   </si>
   <si>
     <t>Cierre Fase 1B.5 — endpoints CRUD (taxonomy + documents + sessions + dashboard)</t>
+  </si>
+  <si>
+    <t>2026-05-23 01:12:28</t>
+  </si>
+  <si>
+    <t>b687217</t>
+  </si>
+  <si>
+    <t>integration</t>
+  </si>
+  <si>
+    <t>Fase 1B.7-1B.8 backend integration (auth+endpoints+repos) contra PG real</t>
+  </si>
+  <si>
+    <t>2026-05-23 01:12:29</t>
+  </si>
+  <si>
+    <t>unit-frontend</t>
+  </si>
+  <si>
+    <t>Fase 1B.7 frontend post camelCase dispatcher (modo mock)</t>
+  </si>
+  <si>
+    <t>2026-05-23 01:12:30</t>
+  </si>
+  <si>
+    <t>unit-backend</t>
+  </si>
+  <si>
+    <t>Fase 1B.7 backend domain tests post alias_generator=to_camel</t>
+  </si>
+  <si>
+    <t>2026-05-23 01:12:45</t>
+  </si>
+  <si>
+    <t>smoke-api</t>
+  </si>
+  <si>
+    <t>Fase 1B.8 smoke curl: /auth/me x3 roles, /categories, /sessions CRUD, IDOR 404, DELETE 204</t>
   </si>
 </sst>
 </file>
@@ -498,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -743,6 +782,122 @@
         <v>33</v>
       </c>
     </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>46</v>
+      </c>
+      <c r="F9">
+        <v>46</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>8.35</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10">
+        <v>220</v>
+      </c>
+      <c r="F10">
+        <v>220</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>17.75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11">
+        <v>27</v>
+      </c>
+      <c r="F11">
+        <v>27</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0.27</v>
+      </c>
+      <c r="I11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>Fecha</t>
   </si>
@@ -152,6 +152,18 @@
   </si>
   <si>
     <t>Fase 1B.8 smoke curl: /auth/me x3 roles, /categories, /sessions CRUD, IDOR 404, DELETE 204</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:49:59</t>
+  </si>
+  <si>
+    <t>fase-2-agente-langgraph</t>
+  </si>
+  <si>
+    <t>9e39d0b</t>
+  </si>
+  <si>
+    <t>Fase 2 cierre — backend agente LangGraph end-to-end. Modos A/B/C + endpoint SSE con 14 eventos. 420 tests, sin tocar Anthropic real.</t>
   </si>
 </sst>
 </file>
@@ -537,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -898,6 +910,35 @@
         <v>46</v>
       </c>
     </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>420</v>
+      </c>
+      <c r="F13">
+        <v>420</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>27</v>
+      </c>
+      <c r="I13" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
   <si>
     <t>Fecha</t>
   </si>
@@ -164,6 +164,18 @@
   </si>
   <si>
     <t>Fase 2 cierre — backend agente LangGraph end-to-end. Modos A/B/C + endpoint SSE con 14 eventos. 420 tests, sin tocar Anthropic real.</t>
+  </si>
+  <si>
+    <t>2026-05-25 18:45:11</t>
+  </si>
+  <si>
+    <t>fase-3-rag-vectorial</t>
+  </si>
+  <si>
+    <t>f9720ca</t>
+  </si>
+  <si>
+    <t>Fase 3.3 cierre — retriever vector + boost autoritativos + HNSW. 25 unit + 7 integration (TRUNCATE chunks autouse para aislamiento). +32 tests vs 508 baseline.</t>
   </si>
 </sst>
 </file>
@@ -549,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -939,6 +951,35 @@
         <v>50</v>
       </c>
     </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14">
+        <v>540</v>
+      </c>
+      <c r="F14">
+        <v>540</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>36.79</v>
+      </c>
+      <c r="I14" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
   <si>
     <t>Fecha</t>
   </si>
@@ -176,6 +176,15 @@
   </si>
   <si>
     <t>Fase 3.3 cierre — retriever vector + boost autoritativos + HNSW. 25 unit + 7 integration (TRUNCATE chunks autouse para aislamiento). +32 tests vs 508 baseline.</t>
+  </si>
+  <si>
+    <t>2026-05-25 19:00:02</t>
+  </si>
+  <si>
+    <t>374792c</t>
+  </si>
+  <si>
+    <t>Fase 3.4 cierre — hybrid search vector 70% + FTS 30% con CTE única (HNSW + GIN). 27 unit + 10 integration. +37 tests vs 540 baseline.</t>
   </si>
 </sst>
 </file>
@@ -561,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -980,6 +989,35 @@
         <v>54</v>
       </c>
     </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15">
+        <v>577</v>
+      </c>
+      <c r="F15">
+        <v>577</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>36.32</v>
+      </c>
+      <c r="I15" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
   <si>
     <t>Fecha</t>
   </si>
@@ -185,6 +185,15 @@
   </si>
   <si>
     <t>Fase 3.4 cierre — hybrid search vector 70% + FTS 30% con CTE única (HNSW + GIN). 27 unit + 10 integration. +37 tests vs 540 baseline.</t>
+  </si>
+  <si>
+    <t>2026-05-25 19:42:48</t>
+  </si>
+  <si>
+    <t>1661a2d</t>
+  </si>
+  <si>
+    <t>Fase 3.5 cierre — endpoint POST /queries + search_kb real con HybridSearcher. 10 unit + 4 integration + refactor de 29 tests existentes. +19 tests netos vs 577 baseline.</t>
   </si>
 </sst>
 </file>
@@ -570,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1018,6 +1027,35 @@
         <v>57</v>
       </c>
     </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>596</v>
+      </c>
+      <c r="F16">
+        <v>596</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>51.81</v>
+      </c>
+      <c r="I16" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
   <si>
     <t>Fecha</t>
   </si>
@@ -194,6 +194,15 @@
   </si>
   <si>
     <t>Fase 3.5 cierre — endpoint POST /queries + search_kb real con HybridSearcher. 10 unit + 4 integration + refactor de 29 tests existentes. +19 tests netos vs 577 baseline.</t>
+  </si>
+  <si>
+    <t>2026-05-25 20:10:37</t>
+  </si>
+  <si>
+    <t>5eb3a01</t>
+  </si>
+  <si>
+    <t>Fase 3.6 cierre — reindex_all + hooks indexer en generation/index_ingestion. 18 unit reindex + 8 hook tests. +26 tests vs 596 baseline.</t>
   </si>
 </sst>
 </file>
@@ -579,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1056,6 +1065,35 @@
         <v>60</v>
       </c>
     </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17">
+        <v>622</v>
+      </c>
+      <c r="F17">
+        <v>622</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>45.87</v>
+      </c>
+      <c r="I17" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="70">
   <si>
     <t>Fecha</t>
   </si>
@@ -203,6 +203,24 @@
   </si>
   <si>
     <t>Fase 3.6 cierre — reindex_all + hooks indexer en generation/index_ingestion. 18 unit reindex + 8 hook tests. +26 tests vs 596 baseline.</t>
+  </si>
+  <si>
+    <t>2026-05-25 20:29:55</t>
+  </si>
+  <si>
+    <t>28a370c</t>
+  </si>
+  <si>
+    <t>Fase 3.7 cierre — eval module + 20 queries en eval_set.jsonl. recall@5=1.0 precision@1=1.0. +26 tests vs 622 baseline. Fase 3 completa.</t>
+  </si>
+  <si>
+    <t>2026-05-25 20:29:57</t>
+  </si>
+  <si>
+    <t>backend-eval</t>
+  </si>
+  <si>
+    <t>Fase 3.7 eval rag (recall@5=1.0, precision@1=1.0). Determinista — sin Cohere real. Validacion dual con TI diferida a Fase 11.</t>
   </si>
 </sst>
 </file>
@@ -588,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1094,6 +1112,64 @@
         <v>63</v>
       </c>
     </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18">
+        <v>648</v>
+      </c>
+      <c r="F18">
+        <v>648</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>60.24</v>
+      </c>
+      <c r="I18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>2.5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
   <si>
     <t>Fecha</t>
   </si>
@@ -221,6 +221,18 @@
   </si>
   <si>
     <t>Fase 3.7 eval rag (recall@5=1.0, precision@1=1.0). Determinista — sin Cohere real. Validacion dual con TI diferida a Fase 11.</t>
+  </si>
+  <si>
+    <t>2026-05-27 19:30:04</t>
+  </si>
+  <si>
+    <t>fase-4-docs</t>
+  </si>
+  <si>
+    <t>b96fdab</t>
+  </si>
+  <si>
+    <t>Fase 4 cierre — generacion (docx/pptx/xlsx/pdf/md) + extractores + anonimizador + endpoints /ingestion + adapter Blob Azurite + worker. +126 tests vs 648. 4 skipped (Azurite/PG condicionales).</t>
   </si>
 </sst>
 </file>
@@ -606,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1170,6 +1182,35 @@
         <v>69</v>
       </c>
     </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20">
+        <v>774</v>
+      </c>
+      <c r="F20">
+        <v>774</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>49.87</v>
+      </c>
+      <c r="I20" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/docs/test-reports/test-runs.xlsx
+++ b/docs/test-reports/test-runs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="80">
   <si>
     <t>Fecha</t>
   </si>
@@ -233,6 +233,24 @@
   </si>
   <si>
     <t>Fase 4 cierre — generacion (docx/pptx/xlsx/pdf/md) + extractores + anonimizador + endpoints /ingestion + adapter Blob Azurite + worker. +126 tests vs 648. 4 skipped (Azurite/PG condicionales).</t>
+  </si>
+  <si>
+    <t>2026-05-28 19:57:27</t>
+  </si>
+  <si>
+    <t>fase-8-ingesta</t>
+  </si>
+  <si>
+    <t>8a4d7c6</t>
+  </si>
+  <si>
+    <t>Cierre Fase 8 (8.1-8.5) — cola de ingesta completa, 271 tests</t>
+  </si>
+  <si>
+    <t>2026-05-28 19:57:35</t>
+  </si>
+  <si>
+    <t>Cierre Fase 8 — smoke E2E ingestion + regresión total 57 specs</t>
   </si>
 </sst>
 </file>
@@ -618,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1211,6 +1229,64 @@
         <v>73</v>
       </c>
     </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21">
+        <v>271</v>
+      </c>
+      <c r="F21">
+        <v>271</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>25.44</v>
+      </c>
+      <c r="I21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22">
+        <v>57</v>
+      </c>
+      <c r="F22">
+        <v>57</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>107.99</v>
+      </c>
+      <c r="I22" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
